--- a/FLORES DE ESTRADA/Junio/PRORRATEO JUNIO Estrada.xlsx
+++ b/FLORES DE ESTRADA/Junio/PRORRATEO JUNIO Estrada.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79BCAA0-A142-48F8-8571-A7B0652F7C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECDD4D2-AFF9-438B-B2F8-92007265401D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -271,10 +271,10 @@
     <t xml:space="preserve">Antonella </t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 10/06 LIQUIDACION : MAYO</t>
-  </si>
-  <si>
     <t>Federico</t>
+  </si>
+  <si>
+    <t>EXPENSAS - VENCIMIENTO 14/07  LIQUIDACION : JUNIO</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1104,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="67" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B1" s="68"/>
       <c r="C1" s="68"/>
@@ -1285,11 +1285,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F11" s="5">
-        <v>64095.377079999998</v>
+        <v>98107.897020000004</v>
       </c>
       <c r="G11" s="62">
         <f>F11</f>
-        <v>64095.377079999998</v>
+        <v>98107.897020000004</v>
       </c>
       <c r="H11" s="8">
         <f>F11-G11</f>
@@ -1334,23 +1334,23 @@
         <v>3.89</v>
       </c>
       <c r="F12" s="5">
-        <v>423370.11607702024</v>
+        <v>538512.34331379808</v>
       </c>
       <c r="G12" s="62"/>
       <c r="H12" s="8">
         <f t="shared" ref="H12:H34" si="0">F12-G12</f>
-        <v>423370.11607702024</v>
+        <v>538512.34331379808</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" ref="J12:J34" si="1">H12*8.8%</f>
-        <v>37256.570214777785</v>
+        <v>47389.086211614238</v>
       </c>
       <c r="K12" s="44">
         <f>H12+I12+J12</f>
-        <v>460626.68629179802</v>
+        <v>585901.42952541227</v>
       </c>
       <c r="L12" s="5">
         <f>C7*E12/100</f>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="N12" s="44">
         <f>K12+L12+M12</f>
-        <v>538512.34331379808</v>
+        <v>663787.08654741221</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -1382,11 +1382,11 @@
         <v>4</v>
       </c>
       <c r="F13" s="5">
-        <v>58437.839409563472</v>
+        <v>80088.079200000007</v>
       </c>
       <c r="G13" s="62">
         <f>F13</f>
-        <v>58437.839409563472</v>
+        <v>80088.079200000007</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="0"/>
@@ -1433,11 +1433,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F14" s="5">
-        <v>64095.377079999998</v>
+        <v>98107.897020000004</v>
       </c>
       <c r="G14" s="62">
         <f t="shared" ref="G14" si="2">F14</f>
-        <v>64095.377079999998</v>
+        <v>98107.897020000004</v>
       </c>
       <c r="H14" s="8">
         <f t="shared" si="0"/>
@@ -1484,11 +1484,11 @@
         <v>3.89</v>
       </c>
       <c r="F15" s="5">
-        <v>50883.880987999997</v>
+        <v>77885.657021999999</v>
       </c>
       <c r="G15" s="62">
         <f t="shared" ref="G15:G21" si="4">F15</f>
-        <v>50883.880987999997</v>
+        <v>77885.657021999999</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="0"/>
@@ -1535,23 +1535,23 @@
         <v>4</v>
       </c>
       <c r="F16" s="5">
-        <v>52322.756799999996</v>
+        <v>137015.2385984</v>
       </c>
       <c r="G16" s="62"/>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>52322.756799999996</v>
+        <v>137015.2385984</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>4604.4025984</v>
+        <v>12057.340996659201</v>
       </c>
       <c r="K16" s="44">
         <f>H16+J16+I16</f>
-        <v>56927.159398399992</v>
+        <v>149072.57959505921</v>
       </c>
       <c r="L16" s="5">
         <f>C7*E16/100</f>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="N16" s="44">
         <f t="shared" si="3"/>
-        <v>137015.2385984</v>
+        <v>229160.65879505922</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1583,11 +1583,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F17" s="5">
-        <v>64095.377079999998</v>
+        <v>98107.897020000004</v>
       </c>
       <c r="G17" s="62">
         <f t="shared" si="4"/>
-        <v>64095.377079999998</v>
+        <v>98107.897020000004</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="0"/>
@@ -1632,11 +1632,11 @@
         <v>3.89</v>
       </c>
       <c r="F18" s="5">
-        <v>50883.880987999997</v>
+        <v>77885.657021999999</v>
       </c>
       <c r="G18" s="62">
         <f t="shared" si="4"/>
-        <v>50883.880987999997</v>
+        <v>77885.657021999999</v>
       </c>
       <c r="H18" s="8">
         <f t="shared" si="0"/>
@@ -1683,11 +1683,11 @@
         <v>4</v>
       </c>
       <c r="F19" s="5">
-        <v>52322.756799999996</v>
+        <v>80088.079200000007</v>
       </c>
       <c r="G19" s="62">
         <f>F19</f>
-        <v>52322.756799999996</v>
+        <v>80088.079200000007</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="0"/>
@@ -1732,11 +1732,11 @@
         <v>12.66</v>
       </c>
       <c r="F20" s="5">
-        <v>165601.525272</v>
+        <v>-4377.2293319999881</v>
       </c>
       <c r="G20" s="62">
         <f>F20+237000</f>
-        <v>402601.525272</v>
+        <v>232622.77066800001</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="0"/>
@@ -1783,11 +1783,11 @@
         <v>7.75</v>
       </c>
       <c r="F21" s="5">
-        <v>101375.34129999999</v>
+        <v>155170.65345000001</v>
       </c>
       <c r="G21" s="63">
         <f t="shared" si="4"/>
-        <v>101375.34129999999</v>
+        <v>155170.65345000001</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="0"/>
@@ -1828,17 +1828,17 @@
         <v>79</v>
       </c>
       <c r="D22" s="55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" s="1">
         <v>7.51</v>
       </c>
       <c r="F22" s="5">
-        <v>174866.77987817599</v>
+        <v>150365.36869799998</v>
       </c>
       <c r="G22" s="62">
         <f>F22</f>
-        <v>174866.77987817599</v>
+        <v>150365.36869799998</v>
       </c>
       <c r="H22" s="8">
         <f t="shared" si="0"/>
@@ -1883,23 +1883,23 @@
         <v>4.45</v>
       </c>
       <c r="F23" s="5">
-        <v>103616.13454832</v>
+        <v>201832.34249857216</v>
       </c>
       <c r="G23" s="62"/>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
-        <v>103616.13454832</v>
+        <v>201832.34249857216</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>9118.2198402521608</v>
+        <v>17761.246139874351</v>
       </c>
       <c r="K23" s="44">
         <f>H23+J23+I23</f>
-        <v>112734.35438857216</v>
+        <v>219593.58863844653</v>
       </c>
       <c r="L23" s="5">
         <f>C7*E23/100</f>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="N23" s="44">
         <f>K23+L23+M23</f>
-        <v>201832.34249857216</v>
+        <v>308691.5767484465</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1929,11 +1929,11 @@
         <v>6.17</v>
       </c>
       <c r="F24" s="5">
-        <v>80707.852363999991</v>
+        <v>123535.86216600001</v>
       </c>
       <c r="G24" s="62">
         <f>F24</f>
-        <v>80707.852363999991</v>
+        <v>123535.86216600001</v>
       </c>
       <c r="H24" s="8">
         <f t="shared" si="0"/>
@@ -1980,23 +1980,23 @@
         <v>4.45</v>
       </c>
       <c r="F25" s="5">
-        <v>155397.25435222301</v>
+        <v>258171.20084521864</v>
       </c>
       <c r="G25" s="62"/>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
-        <v>155397.25435222301</v>
+        <v>258171.20084521864</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>13674.958382995626</v>
+        <v>22719.065674379242</v>
       </c>
       <c r="K25" s="44">
         <f>H25+J25+I25</f>
-        <v>169072.21273521864</v>
+        <v>280890.26651959791</v>
       </c>
       <c r="L25" s="5">
         <f>C7*E25/100+1</f>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="N25" s="44">
         <f>K25+L25+M25</f>
-        <v>258171.20084521864</v>
+        <v>369989.25462959788</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2028,23 +2028,23 @@
         <v>9.19</v>
       </c>
       <c r="F26" s="5">
-        <v>486959.29469553451</v>
+        <v>713815.07459074154</v>
       </c>
       <c r="G26" s="62"/>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
-        <v>486959.29469553451</v>
+        <v>713815.07459074154</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>42852.417933207042</v>
+        <v>62815.726563985263</v>
       </c>
       <c r="K26" s="44">
         <f>H26+J26+I26</f>
-        <v>529811.71262874152</v>
+        <v>776630.80115472677</v>
       </c>
       <c r="L26" s="5">
         <f>C7*E26/100+1</f>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="N26" s="44">
         <f>K26+L26+M26</f>
-        <v>713815.07459074154</v>
+        <v>960634.16311672679</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2076,11 +2076,11 @@
         <v>1.18</v>
       </c>
       <c r="F27" s="5">
-        <v>15436.213255999999</v>
+        <v>23626.983364</v>
       </c>
       <c r="G27" s="62">
         <f>F27</f>
-        <v>15436.213255999999</v>
+        <v>23626.983364</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="0"/>
@@ -2125,23 +2125,23 @@
         <v>1.18</v>
       </c>
       <c r="F28" s="5">
-        <v>15436.213255999999</v>
+        <v>40421.583386528</v>
       </c>
       <c r="G28" s="62"/>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
-        <v>15436.213255999999</v>
+        <v>40421.583386528</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>1358.386766528</v>
+        <v>3557.0993380144641</v>
       </c>
       <c r="K28" s="44">
         <f t="shared" si="7"/>
-        <v>16794.600022528</v>
+        <v>43978.682724542465</v>
       </c>
       <c r="L28" s="5">
         <f>C7*E28/100+1</f>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="N28" s="44">
         <f t="shared" ref="N28:N34" si="8">K28+L28+M28</f>
-        <v>40421.583386528</v>
+        <v>67605.666088542464</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2171,23 +2171,23 @@
         <v>1.18</v>
       </c>
       <c r="F29" s="5">
-        <v>15436.213255999999</v>
+        <v>40421.583386528</v>
       </c>
       <c r="G29" s="62"/>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
-        <v>15436.213255999999</v>
+        <v>40421.583386528</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>1358.386766528</v>
+        <v>3557.0993380144641</v>
       </c>
       <c r="K29" s="44">
         <f t="shared" si="7"/>
-        <v>16794.600022528</v>
+        <v>43978.682724542465</v>
       </c>
       <c r="L29" s="5">
         <f>C7*E29/100+1</f>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="N29" s="44">
         <f t="shared" si="8"/>
-        <v>40421.583386528</v>
+        <v>67605.666088542464</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2217,25 +2217,25 @@
         <v>1.18</v>
       </c>
       <c r="F30" s="5">
-        <v>62071.494580752566</v>
+        <v>79118.78546785879</v>
       </c>
       <c r="G30" s="62">
         <v>11068</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
-        <v>51003.494580752566</v>
+        <v>68050.78546785879</v>
       </c>
       <c r="I30" s="5">
         <v>0</v>
       </c>
       <c r="J30" s="9">
         <f t="shared" si="1"/>
-        <v>4488.3075231062267</v>
+        <v>5988.4691211715744</v>
       </c>
       <c r="K30" s="44">
         <f t="shared" si="7"/>
-        <v>55491.80210385879</v>
+        <v>74039.254589030359</v>
       </c>
       <c r="L30" s="5">
         <f>C7*E30/100+1</f>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="N30" s="44">
         <f>K30+L30+M30</f>
-        <v>79118.78546785879</v>
+        <v>97666.237953030359</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2265,11 +2265,11 @@
         <v>1.18</v>
       </c>
       <c r="F31" s="5">
-        <v>15436.213255999999</v>
+        <v>23626.983364</v>
       </c>
       <c r="G31" s="62">
         <f t="shared" ref="G31:G33" si="9">F31</f>
-        <v>15436.213255999999</v>
+        <v>23626.983364</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="0"/>
@@ -2314,11 +2314,11 @@
         <v>1.18</v>
       </c>
       <c r="F32" s="5">
-        <v>15436.213255999999</v>
+        <v>23626.983364</v>
       </c>
       <c r="G32" s="62">
         <f>F32</f>
-        <v>15436.213255999999</v>
+        <v>23626.983364</v>
       </c>
       <c r="H32" s="8">
         <f t="shared" si="0"/>
@@ -2363,11 +2363,11 @@
         <v>1.18</v>
       </c>
       <c r="F33" s="5">
-        <v>15436.213255999999</v>
+        <v>23626.983364</v>
       </c>
       <c r="G33" s="62">
         <f t="shared" si="9"/>
-        <v>15436.213255999999</v>
+        <v>23626.983364</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="0"/>
@@ -2409,17 +2409,17 @@
         <v>79</v>
       </c>
       <c r="D34" s="55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E34" s="1">
         <v>1.18</v>
       </c>
       <c r="F34" s="5">
-        <v>27477.827048767998</v>
+        <v>23626.983364</v>
       </c>
       <c r="G34" s="62">
         <f>F34</f>
-        <v>27477.827048767998</v>
+        <v>23626.983364</v>
       </c>
       <c r="H34" s="8">
         <f t="shared" si="0"/>
@@ -2462,15 +2462,15 @@
       </c>
       <c r="F35" s="46">
         <f>SUM(F11:F34)</f>
-        <v>2331198.1458783578</v>
+        <v>3162408.8873936455</v>
       </c>
       <c r="G35" s="61">
         <f>SUM(G11:G34)</f>
-        <v>1264656.6683125077</v>
+        <v>1401168.7353059999</v>
       </c>
       <c r="H35" s="47">
         <f>SUM(H11:H34)</f>
-        <v>1066541.4775658501</v>
+        <v>1761240.1520876456</v>
       </c>
       <c r="I35" s="47">
         <f>SUM(I12:I34)</f>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="J35" s="48">
         <f>SUM(J11:J34)</f>
-        <v>93855.650025794836</v>
+        <v>154989.13338371279</v>
       </c>
       <c r="K35" s="48"/>
       <c r="L35" s="47">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="N35" s="56">
         <f>SUM(N11:N34)</f>
-        <v>3162408.8873936455</v>
+        <v>3918241.045273358</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
